--- a/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dorian arrive au parc avec maman. Maman montre le bac à sable. C'est l'espace montré. Dorian s'assoit. Il sent le sable frais. Maman s'assoit sur le banc. L'adulte voit Dorian. Dorian verse le seau. Il reste dans l'espace montré. Maman dit : je te vois. L'adulte voit. Plus tard, maman montre le toboggan. Autre espace montré. Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.</t>
+          <t>Dorian arrive au parc avec maman. Maman montre le bac à sable. C'est l'espace montré. Dorian s'assoit. Il sent le sable frais. Maman s'assoit sur le banc. L'adulte voit Dorian. Dorian verse le seau. Il reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, maman montre le toboggan. Autre espace montré. Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dorian arrive au parc avec maman. Maman montre le bac à sable. C'est l'espace montré. Dorian s'assoit. Il sent le sable frais. Maman s'assoit sur le banc. L'adulte voit Dorian. Dorian verse le seau. Il reste dans l'espace montré.
+maman|Je te vois. L'adulte voit. Plus tard, maman montre le toboggan. Autre espace montré.
+narrateur|Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dorian joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dorian est resté dans l'espace montré. Au bac, puis au toboggan. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dorian prend la main de maman. Ils quittent le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1503,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Dorian joue au parc. Où reste-t-il ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -1666,6 +1681,7 @@
           <t>narrateur|Dorian est resté dans l'espace montré. Au bac, puis au toboggan. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1849,11 @@
           <t>narrateur|Dorian prend la main de maman. Ils quittent le parc.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dorian joue où maman voit</t>
+          <t>Le toboggan d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss joue au bac puis au toboggan, toujours dans l'espace que maman a montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dorian arrive au parc avec maman. Maman montre le bac à sable. C'est l'espace montré. Dorian s'assoit. Il sent le sable frais. Maman s'assoit sur le banc. L'adulte voit Dorian. Dorian verse le seau. Il reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, maman montre le toboggan. Autre espace montré. Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.</t>
+          <t>La chaîne de la balançoire fait tic. Le parc sent le pin chaud. Une pomme de pin roule sur le chemin. Les aiguilles sont sèches sous les pieds. Un banc gris attend à l'ombre. Maman pose le sac sur le banc. Tu as entendu la chaîne, Aniss ? Oui, maman. Ça fait tic. En ce moment, maman montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, maman ? Oui. On reste dans l'espace montré. Aniss s'assoit. Il sent le sable frais. Maman s'assoit sur le banc gris. L'adulte voit Aniss. Aniss verse le seau. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le sable coule entre les doigts. Il est un peu froid, tout fin. Ça coule. Oui. Tu joues là où l'adulte a dit. Plus tard, maman montre le toboggan. Autre espace montré. Ici, l'adulte voit encore. Je peux glisser ? Oui. Tu restes dans l'espace montré. Aniss grimpe l'échelle. Les barreaux sont lisses et tièdes. Il glisse. Le plastique fait un petit chuintement. Il revient au pied. Maman le voit encore. L'adulte voit. Encore une fois ? Oui. Dans l'espace montré. Aniss glisse encore. Il reste là où maman a dit. Tu restes là où l'adulte a dit ? Oui. Bravo, Aniss. Tu as fait du bon travail. La chaîne fait encore tic, au loin. Aniss range le seau près du bac. Il reste dans l'espace montré. Tu as fini de glisser ? Oui, maman. Bravo. Une aiguille de pin colle à son genou. Aniss la retire, tout doux. Ça pique un peu. Oui. Tu restes ici. L'adulte voit. Le toboggan brille encore. Aniss touche le plastique tiède. Il est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dorian arrive au parc avec maman. Maman montre le bac à sable. C'est l'espace montré. Dorian s'assoit. Il sent le sable frais. Maman s'assoit sur le banc. L'adulte voit Dorian. Dorian verse le seau. Il reste dans l'espace montré.
-maman|Je te vois. L'adulte voit. Plus tard, maman montre le toboggan. Autre espace montré.
-narrateur|Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.</t>
+          <t>narrateur|La chaîne de la balançoire fait tic.
+narrateur|Le parc sent le pin chaud.
+narrateur|Une pomme de pin roule sur le chemin.
+narrateur|Les aiguilles sont sèches sous les pieds.
+narrateur|Un banc gris attend à l'ombre.
+narrateur|Maman pose le sac sur le banc.
+maman|Tu as entendu la chaîne, Aniss ?
+enfant-m|Oui, maman.
+enfant-m|Ça fait tic.
+narrateur|En ce moment, maman montre le bac à sable.
+maman|C'est l'espace montré.
+maman|Tu joues ici.
+maman|L'adulte voit.
+enfant-m|Ici, maman ?
+maman|Oui.
+maman|On reste dans l'espace montré.
+narrateur|Aniss s'assoit.
+narrateur|Il sent le sable frais.
+narrateur|Maman s'assoit sur le banc gris.
+narrateur|L'adulte voit Aniss.
+narrateur|Aniss verse le seau.
+narrateur|Il reste dans l'espace montré.
+maman|Je te vois.
+maman|L'adulte voit.
+enfant-m|Tu me vois ?
+maman|Oui.
+narrateur|Le sable coule entre les doigts.
+narrateur|Il est un peu froid, tout fin.
+enfant-m|Ça coule.
+maman|Oui.
+maman|Tu joues là où l'adulte a dit.
+narrateur|Plus tard, maman montre le toboggan.
+maman|Autre espace montré.
+maman|Ici, l'adulte voit encore.
+enfant-m|Je peux glisser ?
+maman|Oui.
+maman|Tu restes dans l'espace montré.
+narrateur|Aniss grimpe l'échelle.
+narrateur|Les barreaux sont lisses et tièdes.
+narrateur|Il glisse.
+narrateur|Le plastique fait un petit chuintement.
+narrateur|Il revient au pied.
+narrateur|Maman le voit encore.
+narrateur|L'adulte voit.
+enfant-m|Encore une fois ?
+maman|Oui.
+maman|Dans l'espace montré.
+narrateur|Aniss glisse encore.
+narrateur|Il reste là où maman a dit.
+maman|Tu restes là où l'adulte a dit ?
+enfant-m|Oui.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|La chaîne fait encore tic, au loin.
+narrateur|Aniss range le seau près du bac.
+narrateur|Il reste dans l'espace montré.
+maman|Tu as fini de glisser ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Une aiguille de pin colle à son genou.
+narrateur|Aniss la retire, tout doux.
+enfant-m|Ça pique un peu.
+maman|Oui.
+maman|Tu restes ici.
+narrateur|L'adulte voit.
+narrateur|Le toboggan brille encore.
+narrateur|Aniss touche le plastique tiède.
+enfant-m|Il est lisse.
+maman|Oui.
+maman|Tu as glissé dans l'espace montré.
+enfant-m|Dans l'espace montré.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1427,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dorian joue au parc. Où reste-t-il ?</t>
+          <t>Aniss joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1583,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dorian joue au parc. Où reste-t-il ?</t>
+          <t>narrateur|Aniss joue au parc.
+narrateur|Où reste-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1534,7 +1616,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dorian est resté dans l'espace montré. Au bac, puis au toboggan. L'adulte voit.</t>
+          <t>Aniss est resté dans l'espace montré. Au bac, puis au toboggan. L'adulte voit. Tu es resté dans l'espace montré ? Oui. Au bac, puis au toboggan. Bravo. L'adulte voit. La pomme de pin est encore sur le chemin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1760,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dorian est resté dans l'espace montré. Au bac, puis au toboggan. L'adulte voit.</t>
+          <t>narrateur|Aniss est resté dans l'espace montré.
+narrateur|Au bac, puis au toboggan.
+narrateur|L'adulte voit.
+maman|Tu es resté dans l'espace montré ?
+enfant-m|Oui.
+enfant-m|Au bac, puis au toboggan.
+maman|Bravo.
+maman|L'adulte voit.
+narrateur|La pomme de pin est encore sur le chemin.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1796,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dorian prend la main de maman. Ils quittent le parc.</t>
+          <t>Aniss prend la main de maman. Tu as fini de ranger ? Oui, maman. Bravo. Papa arrive près des pins. Vous avez joué ici ? Oui, papa. Dans l'espace montré. L'adulte voit. Ils quittent le parc. Les aiguilles craquent sous les pas.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1936,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dorian prend la main de maman. Ils quittent le parc.</t>
+          <t>narrateur|Aniss prend la main de maman.
+maman|Tu as fini de ranger ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Papa arrive près des pins.
+papa|Vous avez joué ici ?
+enfant-m|Oui, papa.
+maman|Dans l'espace montré.
+papa|L'adulte voit.
+narrateur|Ils quittent le parc.
+narrateur|Les aiguilles craquent sous les pas.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1878,7 +1978,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La chaîne de la balançoire se tait. On a glissé. Oui. Dans l'espace montré. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2118,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La chaîne de la balançoire se tait.
+enfant-m|On a glissé.
+maman|Oui.
+maman|Dans l'espace montré.
+maman|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2183,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La chaîne de la balançoire fait tic. Le parc sent le pin chaud. Une pomme de pin roule sur le chemin. Les aiguilles sont sèches sous les pieds. Un banc gris attend à l'ombre. Maman pose le sac sur le banc. Tu as entendu la chaîne, Aniss ? Oui, maman. Ça fait tic. En ce moment, maman montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, maman ? Oui. On reste dans l'espace montré. Aniss s'assoit. Il sent le sable frais. Maman s'assoit sur le banc gris. L'adulte voit Aniss. Aniss verse le seau. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le sable coule entre les doigts. Il est un peu froid, tout fin. Ça coule. Oui. Tu joues là où l'adulte a dit. Plus tard, maman montre le toboggan. Autre espace montré. Ici, l'adulte voit encore. Je peux glisser ? Oui. Tu restes dans l'espace montré. Aniss grimpe l'échelle. Les barreaux sont lisses et tièdes. Il glisse. Le plastique fait un petit chuintement. Il revient au pied. Maman le voit encore. L'adulte voit. Encore une fois ? Oui. Dans l'espace montré. Aniss glisse encore. Il reste là où maman a dit. Tu restes là où l'adulte a dit ? Oui. Bravo, Aniss. Tu as fait du bon travail. La chaîne fait encore tic, au loin. Aniss range le seau près du bac. Il reste dans l'espace montré. Tu as fini de glisser ? Oui, maman. Bravo. Une aiguille de pin colle à son genou. Aniss la retire, tout doux. Ça pique un peu. Oui. Tu restes ici. L'adulte voit. Le toboggan brille encore. Aniss touche le plastique tiède. Il est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo.</t>
+          <t>La chaîne de la balançoire fait tic. Le parc sent le pin chaud. Une pomme de pin roule sur le chemin. Les aiguilles sont sèches sous les pieds. Un banc gris attend à l'ombre. Maman pose le sac sur le banc. Tu as entendu la chaîne, Aniss ? Oui, maman. Ça fait tic. En ce moment, maman montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, maman ? Oui. On reste dans l'espace montré. Aniss s'assoit. Il sent le sable frais. Maman s'assoit sur le banc gris. L'adulte voit Aniss. Aniss verse le seau. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le sable coule entre les doigts. Il est un peu froid, tout fin. Ça coule. Oui. Tu joues là où l'adulte a dit. Plus tard, maman montre le toboggan. Autre espace montré. Ici, l'adulte voit encore. Je peux glisser ? Oui. Tu restes dans l'espace montré. Aniss grimpe l'échelle. Les barreaux sont lisses et tièdes. Il glisse. Le plastique fait un petit chuintement. Il revient au pied. Maman le voit encore. L'adulte voit. Encore une fois ? Oui. Dans l'espace montré. Aniss glisse encore. Il reste là où maman a dit. Tu restes là où l'adulte a dit ? Oui. Bravo, Aniss. La chaîne fait encore tic, au loin. Aniss range le seau près du bac. Il reste dans l'espace montré. Tu as fini de glisser ? Oui, maman. Bravo. Une aiguille de pin colle à son genou. Aniss la retire, tout doux. Ça pique un peu. Oui. Tu restes ici. L'adulte voit. Le toboggan brille encore. Aniss touche le plastique tiède. Il est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dorian arrive au parc avec maman. Maman montre le bac à sable. C'est l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Dorian s'assoit. Il sent le sable frais. Maman s'assoit sur le banc. L'adulte voit Dorian. Dorian verse le seau. Il reste dans l'espace montré. Maman dit : je te vois. L'adulte voit. Plus tard, maman montre le toboggan. Autre espace montré. Dorian grimpe l'échelle. Il glisse. Il revient au pied. Maman le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Papa arrivera après. Dorian range le seau. Il reste là où maman a dit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La chaîne de la balançoire fait tic. Le parc sent le pin chaud. Une pomme de pin roule sur le chemin. Les aiguilles sont sèches sous les pieds. Un banc gris attend à l'ombre. Maman pose le sac sur le banc. Tu as entendu la chaîne, Aniss ? Oui, maman. Ça fait tic. En ce moment, maman montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, maman ? Oui. On reste dans l'espace montré. Aniss s'assoit. Il sent le sable frais. Maman s'assoit sur le banc gris. L'adulte voit Aniss. Aniss verse le seau. Il reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le sable coule entre les doigts. Il est un peu froid, tout fin. Ça coule. Oui. Tu joues là où l'adulte a dit. Plus tard, maman montre le toboggan. Autre espace montré. Ici, l'adulte voit encore. Je peux glisser ? Oui. Tu restes dans l'espace montré. Aniss grimpe l'échelle. Les barreaux sont lisses et tièdes. Il glisse. Le plastique fait un petit chuintement. Il revient au pied. Maman le voit encore. L'adulte voit. Encore une fois ? Oui. Dans l'espace montré. Aniss glisse encore. Il reste là où maman a dit. Tu restes là où l'adulte a dit ? Oui. Bravo, Aniss. La chaîne fait encore tic, au loin. Aniss range le seau près du bac. Il reste dans l'espace montré. Tu as fini de glisser ? Oui, maman. Bravo. Une aiguille de pin colle à son genou. Aniss la retire, tout doux. Ça pique un peu. Oui. Tu restes ici. L'adulte voit. Le toboggan brille encore. Aniss touche le plastique tiède. Il est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1376,7 +1376,6 @@
 maman|Tu restes là où l'adulte a dit ?
 enfant-m|Oui.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
 narrateur|La chaîne fait encore tic, au loin.
 narrateur|Aniss range le seau près du bac.
 narrateur|Il reste dans l'espace montré.
@@ -1432,7 +1431,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dorian joue au parc. Où reste-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1621,7 +1620,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dorian est resté dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Au bac, puis au toboggan. L'adulte voit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss est resté dans l'espace montré. Au bac, puis au toboggan. L'adulte voit. Tu es resté dans l'espace montré ? Oui. Au bac, puis au toboggan. Bravo. L'adulte voit. La pomme de pin est encore sur le chemin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1771,7 +1770,6 @@
 narrateur|La pomme de pin est encore sur le chemin.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1801,7 +1799,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dorian prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils quittent le parc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss prend la main de maman. Tu as fini de ranger ? Oui, maman. Bravo. Papa arrive près des pins. Vous avez joué ici ? Oui, papa. Dans l'espace montré. L'adulte voit. Ils quittent le parc. Les aiguilles craquent sous les pas.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1978,12 +1976,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La chaîne de la balançoire se tait. On a glissé. Oui. Dans l'espace montré. Bravo, Aniss. L'histoire est finie.</t>
+          <t>La chaîne de la balançoire se tait. On a glissé. Oui. Dans l'espace montré. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La chaîne de la balançoire se tait. On a glissé. Oui. Dans l'espace montré. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2122,11 +2120,9 @@
 enfant-m|On a glissé.
 maman|Oui.
 maman|Dans l'espace montré.
-maman|Bravo, Aniss.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Aniss.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2145,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2186,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-10.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dorian, maman</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
